--- a/data/charlas-sinteticas.xlsx
+++ b/data/charlas-sinteticas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charlas" sheetId="1" r:id="R03e9816ebb644c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charlas" sheetId="1" r:id="R146eab4fa69b4b7f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,10 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +33,14 @@
       <x:color rgb="FF1E293B"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,8 +52,13 @@
         <x:fgColor rgb="FF0E7490"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF7900"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -98,13 +110,27 @@
       </x:right>
       <x:bottom style="thin">
         <x:color rgb="FFCBD5E1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE1E5E9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE1E5E9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE1E5E9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE1E5E9"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -143,6 +169,37 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -359,254 +416,578 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" hidden="0" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="25" t="str">
+        <x:v>Año</x:v>
+      </x:c>
+      <x:c r="B1" s="25" t="str">
         <x:v>Region</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="C1" s="25" t="str">
         <x:v>Lugar</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="D1" s="25" t="str">
         <x:v>ColegioLocacion</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="E1" s="25" t="str">
         <x:v>CantidaddeAlumnos</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>Arica y Parinacota</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>Arica</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
-        <x:v>Colegio San Marcos</x:v>
-      </x:c>
-      <x:c r="D2" s="12" t="n">
+      <x:c r="A2" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B2" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="str">
+        <x:v>Escuela Gendarmería</x:v>
+      </x:c>
+      <x:c r="E2" s="28" t="n">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B3" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C3" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D3" s="27" t="str">
+        <x:v>Escuela Marques de Ovando</x:v>
+      </x:c>
+      <x:c r="E3" s="28" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B4" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C4" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="str">
+        <x:v>Escuela Villaseca</x:v>
+      </x:c>
+      <x:c r="E4" s="28" t="n">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B5" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C5" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>Escuela Humberto Moreno</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="n">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B6" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C6" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D6" s="27" t="str">
+        <x:v>Escuela Politécnica Aeronáutica FACH</x:v>
+      </x:c>
+      <x:c r="E6" s="28" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B7" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C7" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D7" s="27" t="str">
+        <x:v>Liceo Nuestra Sra. de las Mercedes</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="n">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B8" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C8" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="str">
+        <x:v>Dirigentes Sindicato de la FTC CODELCO</x:v>
+      </x:c>
+      <x:c r="E8" s="28" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B9" s="27" t="str">
+        <x:v>Los Lagos</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="str">
+        <x:v>Puerto Montt</x:v>
+      </x:c>
+      <x:c r="D9" s="27" t="str">
+        <x:v>AIEP Dirigentes Sociales</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="n">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B10" s="27" t="str">
+        <x:v>O'Higgins</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="str">
+        <x:v>Paredones</x:v>
+      </x:c>
+      <x:c r="D10" s="27" t="str">
+        <x:v>Escuela Mercedes Urzua</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="n">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B11" s="27" t="str">
+        <x:v>Coquimbo</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="str">
+        <x:v>Vicuña</x:v>
+      </x:c>
+      <x:c r="D11" s="27" t="str">
+        <x:v>Escuela Juan Rendic</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="n">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B12" s="27" t="str">
+        <x:v>Coquimbo</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="str">
+        <x:v>Vicuña</x:v>
+      </x:c>
+      <x:c r="D12" s="27" t="str">
+        <x:v>Escuela Federico Barnes Payne</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B13" s="27" t="str">
+        <x:v>Coquimbo</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="str">
+        <x:v>Vicuña</x:v>
+      </x:c>
+      <x:c r="D13" s="27" t="str">
+        <x:v>Escuela Neftali Reyes Basoalto</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B14" s="27" t="str">
+        <x:v>Coquimbo</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="str">
+        <x:v>La Serena</x:v>
+      </x:c>
+      <x:c r="D14" s="27" t="str">
+        <x:v>AIEP Dirigentes Sociales</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B15" s="27" t="str">
+        <x:v>Magallanes</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="str">
+        <x:v>Punta Arenas</x:v>
+      </x:c>
+      <x:c r="D15" s="27" t="str">
+        <x:v>Liceo Polivalente Sara Braun</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B16" s="27" t="str">
+        <x:v>Magallanes</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="str">
+        <x:v>Punta Arenas</x:v>
+      </x:c>
+      <x:c r="D16" s="27" t="str">
+        <x:v>Escuela Pedro Sarmiento de Gamboa</x:v>
+      </x:c>
+      <x:c r="E16" s="28" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B17" s="27" t="str">
+        <x:v>Magallanes</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="str">
+        <x:v>Punta Arenas</x:v>
+      </x:c>
+      <x:c r="D17" s="27" t="str">
+        <x:v>Escuela Dieciocho de Septiembre</x:v>
+      </x:c>
+      <x:c r="E17" s="28" t="n">
         <x:v>96</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="11" t="str">
+    <x:row r="18">
+      <x:c r="A18" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B18" s="27" t="str">
+        <x:v>Magallanes</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="str">
+        <x:v>Punta Arenas</x:v>
+      </x:c>
+      <x:c r="D18" s="27" t="str">
+        <x:v>Escuela Patagonia</x:v>
+      </x:c>
+      <x:c r="E18" s="28" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B19" s="27" t="str">
+        <x:v>Magallanes</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="str">
+        <x:v>Punta Arenas</x:v>
+      </x:c>
+      <x:c r="D19" s="27" t="str">
+        <x:v>Escuela Portugal</x:v>
+      </x:c>
+      <x:c r="E19" s="28" t="n">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="26" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B20" s="27" t="str">
+        <x:v>Biobío</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="str">
+        <x:v>Concepción</x:v>
+      </x:c>
+      <x:c r="D20" s="27" t="str">
+        <x:v>Sindicato SIL Walmart</x:v>
+      </x:c>
+      <x:c r="E20" s="28" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B21" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D21" s="27" t="str">
+        <x:v>Escuela Particular N°46 Graciela Letelier de Ibáñez</x:v>
+      </x:c>
+      <x:c r="E21" s="28" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B22" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D22" s="27" t="str">
+        <x:v>Jardín Infantil Colón (BancoEstado)</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B23" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D23" s="27" t="str">
+        <x:v>Liceo Profesional Abdón Cifuentes</x:v>
+      </x:c>
+      <x:c r="E23" s="28" t="n">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B24" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D24" s="27" t="str">
+        <x:v>Escuela Lazaro de la Salle</x:v>
+      </x:c>
+      <x:c r="E24" s="28" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B25" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D25" s="27" t="str">
+        <x:v>Alumnos de la Academia Politécnica Aeronáutica</x:v>
+      </x:c>
+      <x:c r="E25" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B26" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D26" s="27" t="str">
+        <x:v>Colegio Sagrados Corazones</x:v>
+      </x:c>
+      <x:c r="E26" s="28" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="26" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B27" s="27" t="str">
         <x:v>Tarapacá</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str">
+      <x:c r="C27" s="27" t="str">
         <x:v>Iquique</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>Liceo Bicentenario Juan Pablo II</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="n">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="11" t="str">
-        <x:v>Antofagasta</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="str">
-        <x:v>Antofagasta</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>Colegio Santa Emilia</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="n">
-        <x:v>112</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Antofagasta</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="str">
-        <x:v>Calama</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="str">
-        <x:v>Liceo América</x:v>
-      </x:c>
-      <x:c r="D5" s="12" t="n">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Coquimbo</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="str">
-        <x:v>La Serena</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="str">
-        <x:v>Colegio Gabriela Mistral</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="n">
-        <x:v>142</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="11" t="str">
-        <x:v>Valparaíso</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
-        <x:v>Valparaíso</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="str">
-        <x:v>Liceo Eduardo de la Barra</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="n">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="11" t="str">
-        <x:v>Valparaíso</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="str">
-        <x:v>Quilpué</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="str">
-        <x:v>Colegio Los Pinos</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="n">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Metropolitana de Santiago</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>Santiago</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>Liceo República de Brasil</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="n">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="11" t="str">
-        <x:v>Metropolitana de Santiago</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="str">
-        <x:v>Puente Alto</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="str">
-        <x:v>Colegio Monte Andino</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="n">
-        <x:v>121</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="11" t="str">
+      <x:c r="D27" s="27" t="str">
+        <x:v>Liceo María Auxiliadora</x:v>
+      </x:c>
+      <x:c r="E27" s="28" t="n">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B28" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D28" s="27" t="str">
+        <x:v>Jardín Infantil Colón (BancoEstado)</x:v>
+      </x:c>
+      <x:c r="E28" s="28" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B29" s="27" t="str">
+        <x:v>Metropolitana de Santiago</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="str">
+        <x:v>RM</x:v>
+      </x:c>
+      <x:c r="D29" s="27" t="str">
+        <x:v>Escuela Consolidada Dávila</x:v>
+      </x:c>
+      <x:c r="E29" s="28" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B30" s="27" t="str">
         <x:v>O'Higgins</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>Rancagua</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>Instituto O'Higgins</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="n">
-        <x:v>109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="11" t="str">
-        <x:v>Maule</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="str">
-        <x:v>Talca</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="str">
-        <x:v>Liceo Abate Molina</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="n">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="11" t="str">
-        <x:v>Ñuble</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="str">
-        <x:v>Chillán</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="str">
-        <x:v>Colegio Bicentenario Padre Hurtado</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="n">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="11" t="str">
-        <x:v>Biobío</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:v>Concepción</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="str">
-        <x:v>Liceo Enrique Molina</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="n">
-        <x:v>178</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="11" t="str">
-        <x:v>Biobío</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="str">
-        <x:v>Los Ángeles</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="str">
-        <x:v>Colegio San Rafael Arcángel</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="n">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="11" t="str">
-        <x:v>La Araucanía</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="str">
-        <x:v>Temuco</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="str">
-        <x:v>Liceo Pablo Neruda</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="n">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="13" t="str">
-        <x:v>Los Lagos</x:v>
-      </x:c>
-      <x:c r="B17" s="14" t="str">
-        <x:v>Puerto Montt</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="str">
-        <x:v>Colegio Pumahue</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="n">
-        <x:v>127</x:v>
+      <x:c r="C30" s="27" t="str">
+        <x:v>Paredones</x:v>
+      </x:c>
+      <x:c r="D30" s="27" t="str">
+        <x:v>Escuela Santa Ana de la Población</x:v>
+      </x:c>
+      <x:c r="E30" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B31" s="27" t="str">
+        <x:v>O'Higgins</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="str">
+        <x:v>Paredones</x:v>
+      </x:c>
+      <x:c r="D31" s="27" t="str">
+        <x:v>Escuela Esmeralda de Cabecera</x:v>
+      </x:c>
+      <x:c r="E31" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B32" s="27" t="str">
+        <x:v>O'Higgins</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="str">
+        <x:v>Paredones</x:v>
+      </x:c>
+      <x:c r="D32" s="27" t="str">
+        <x:v>Escuela las Carmelitas de El Quillay</x:v>
+      </x:c>
+      <x:c r="E32" s="28" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B33" s="27" t="str">
+        <x:v>O'Higgins</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="str">
+        <x:v>Paredones</x:v>
+      </x:c>
+      <x:c r="D33" s="27" t="str">
+        <x:v>Escuela San Pedro de El Portero</x:v>
+      </x:c>
+      <x:c r="E33" s="28" t="n">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R985c972c700c4552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2670791596d74b90"/>
   </x:tableParts>
 </x:worksheet>
 </file>